--- a/4578 Otsuka.xlsx
+++ b/4578 Otsuka.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA1E4A3-7570-4A62-84DC-4B256E0EECF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E51F40-B3BF-4A70-9540-C1CB48ED9A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50100" yWindow="2280" windowWidth="22875" windowHeight="18315" xr2:uid="{8AEC93ED-DE78-43E1-A3CC-6845D1322955}"/>
+    <workbookView xWindow="350" yWindow="1040" windowWidth="19050" windowHeight="19840" xr2:uid="{8AEC93ED-DE78-43E1-A3CC-6845D1322955}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -57,9 +57,6 @@
     <t>EV JPY</t>
   </si>
   <si>
-    <t>Q224</t>
-  </si>
-  <si>
     <t>Acquires Jnana.</t>
   </si>
   <si>
@@ -118,6 +115,9 @@
   </si>
   <si>
     <t>R&amp;D</t>
+  </si>
+  <si>
+    <t>Q226</t>
   </si>
 </sst>
 </file>
@@ -500,14 +500,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC15A73-670F-4BC4-AE3C-79C8EBD781A0}">
   <dimension ref="B2:M13"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="12" max="12" width="12.85546875" customWidth="1"/>
+    <col min="12" max="12" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
         <v>0</v>
@@ -516,77 +516,77 @@
         <v>8383</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K3" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="3">
-        <v>542.72572500000001</v>
+        <v>527.08410900000001</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K4" t="s">
         <v>2</v>
       </c>
       <c r="L4" s="1">
         <f>+L2*L3</f>
-        <v>4549669.7526749996</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+        <v>4418546.0857469998</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K5" t="s">
         <v>3</v>
       </c>
       <c r="L5" s="1">
-        <f>485892+220335+105160+310410</f>
-        <v>1121797</v>
+        <f>469548+36393+373116+238006</f>
+        <v>1117063</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s">
         <v>4</v>
       </c>
       <c r="L6" s="1">
-        <f>98576+67900+20322</f>
-        <v>186798</v>
+        <f>87257+69895+7399+12477</f>
+        <v>177028</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s">
         <v>5</v>
       </c>
       <c r="L7" s="1">
         <f>+L4-L5+L6</f>
-        <v>3614670.7526749996</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+        <v>3478511.0857469998</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="H13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -597,35 +597,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F37725E7-BC53-408E-80B2-CC7BAA2C4AF9}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="9.140625" style="2"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>14</v>
       </c>
       <c r="C3" s="2">
         <v>650442</v>
@@ -634,9 +634,9 @@
         <v>766728</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2">
         <v>226208</v>
@@ -645,9 +645,9 @@
         <v>271826</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2">
         <v>17425</v>
@@ -656,9 +656,9 @@
         <v>15670</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="5">
         <v>947537</v>
@@ -669,9 +669,9 @@
       </c>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2">
         <v>287862</v>
@@ -680,9 +680,9 @@
         <v>316211</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2">
         <f>+C6-C7</f>
@@ -693,9 +693,9 @@
         <v>792719</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" s="2">
         <v>372283</v>
@@ -704,9 +704,9 @@
         <v>453722</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2">
         <v>143949</v>
